--- a/Compititor's_Price/Novia_Prices/Novia_Prices_18-09-2026.xlsx
+++ b/Compititor's_Price/Novia_Prices/Novia_Prices_18-09-2026.xlsx
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>£12.95</t>
+          <t>£14.20</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>£12.95</t>
+          <t>£14.99</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
